--- a/public/asset/bulkEmailerTemplate.xlsx
+++ b/public/asset/bulkEmailerTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ajaz\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F08867-EF33-41E4-8CEA-3E67B4A445F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D513EE95-9D3A-44DF-A0A1-00CA89EEBAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Name</t>
   </si>
@@ -33,33 +33,6 @@
     <t>Email</t>
   </si>
   <si>
-    <t>Rashid</t>
-  </si>
-  <si>
-    <t>r1@mckinsol.com</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>ashok@mckinsol.com</t>
-  </si>
-  <si>
-    <t>UI?UX</t>
-  </si>
-  <si>
-    <t>Ashok</t>
-  </si>
-  <si>
-    <t>Tarun</t>
-  </si>
-  <si>
-    <t>ttomar@mckinsol.com</t>
-  </si>
-  <si>
-    <t>Angular</t>
-  </si>
-  <si>
     <t>Contact No</t>
   </si>
   <si>
@@ -72,20 +45,20 @@
     <t>Skills</t>
   </si>
   <si>
-    <t>Python</t>
-  </si>
-  <si>
-    <t>version2</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> html,css</t>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Visa</t>
+  </si>
+  <si>
+    <t>Experience</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,14 +71,6 @@
       <color rgb="FF1D1C1D"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -125,18 +90,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -415,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
@@ -424,7 +386,7 @@
     <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,100 +394,40 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>9080988978</v>
-      </c>
-      <c r="D2" s="1">
-        <v>9080988978</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <v>9022988978</v>
-      </c>
-      <c r="D4" s="1">
-        <v>9022988978</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>9033988978</v>
-      </c>
-      <c r="D5" s="1">
-        <v>90330988978</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{2CAB565A-08CB-43E9-AB83-21ED641B835B}"/>
-    <hyperlink ref="B4" r:id="rId2" xr:uid="{025A3051-0EEC-4A0E-BB60-7A29AE72D45C}"/>
-    <hyperlink ref="B5" r:id="rId3" xr:uid="{F7B78038-0985-4069-82EA-6185E6858655}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/asset/bulkEmailerTemplate.xlsx
+++ b/public/asset/bulkEmailerTemplate.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ajaz\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ajaz\Desktop\BulkMailer\bulk_emailer_frontend\public\asset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D513EE95-9D3A-44DF-A0A1-00CA89EEBAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{262718E5-1727-4928-8B00-DC9378738098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
